--- a/artfynd/A 25155-2026 artfynd.xlsx
+++ b/artfynd/A 25155-2026 artfynd.xlsx
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117637</v>
+        <v>114429</v>
       </c>
       <c r="B2" t="n">
-        <v>103225</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106205</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556407.0512200693</v>
+        <v>556407</v>
       </c>
       <c r="R2" t="n">
-        <v>6390314.264478275</v>
+        <v>6390314</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -743,29 +738,24 @@
           <t>Frödinge</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Hf-Vim-1034</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1995-07-07</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1985-01-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1995-07-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1985-12-31</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Observatör: Thore Andersson.</t>
+          <t>Observatör: Thore Andersson. 1985 ca.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,19 +791,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124606</v>
+        <v>117636</v>
       </c>
       <c r="B3" t="n">
-        <v>103225</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106205</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -834,26 +819,17 @@
           <t>(L.) W. P. C. Barton</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Nyn, väststranden, 400 m N om sockengränsen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556403.4038069368</v>
+        <v>556403</v>
       </c>
       <c r="R3" t="n">
-        <v>6390614.435756212</v>
+        <v>6390614</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -885,27 +861,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2002-07-14</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1995-07-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2002-07-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1995-07-07</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Observatör: Thore Andersson. Igenväxning. Ej blommande.</t>
+          <t>Observatör: Thore Andersson. Ny lokal.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -941,14 +907,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74119953</v>
+        <v>74119948</v>
       </c>
       <c r="B4" t="n">
-        <v>105693</v>
+        <v>106204</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -972,14 +938,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nyns väststrand vid sockengränsen, Sm</t>
+          <t>Nyns väststrand  400 m N sockengränsen, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556402</v>
+        <v>556399</v>
       </c>
       <c r="R4" t="n">
-        <v>6390309</v>
+        <v>6390609</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1006,17 +972,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1983-01-01</t>
+          <t>1995-07-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1987-12-31</t>
+          <t>1995-07-07</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6G8b 1833. SOM: Chimaphila umbellata. LEG: Thore Andersson</t>
+          <t>Smålands flora 2007: KOO: 6G8b 2133. SOM: Chimaphila umbellata. LEG: Thore Andersson. KOM: Ca 20 blommande ex</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,7 +996,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Tallskog på sandsediment</t>
+          <t>Barr-lövskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1052,14 +1018,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>74119950</v>
+        <v>74119952</v>
       </c>
       <c r="B5" t="n">
-        <v>105693</v>
+        <v>106204</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1083,14 +1049,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nyns väststrand  400 m N sockengränsen, Sm</t>
+          <t>Nyns väststrand vid sockengränsen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556399</v>
+        <v>556402</v>
       </c>
       <c r="R5" t="n">
-        <v>6390609</v>
+        <v>6390309</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1117,17 +1083,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2002-07-14</t>
+          <t>1995-07-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2002-07-14</t>
+          <t>1995-07-07</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 6G8b 2133. SOM: Chimaphila umbellata. LEG: Thore Andersson. KOM: 15</t>
+          <t>Smålands flora 2007: KOO: 6G8b 1833. SOM: Chimaphila umbellata. LEG: Thore Andersson. KOM: Ca 5 ex, el blommande</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,7 +1107,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Barr-lövskog</t>
+          <t>Tallskog på sandsediment</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1166,7 +1132,7 @@
         <v>74861045</v>
       </c>
       <c r="B6" t="n">
-        <v>105732</v>
+        <v>106243</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 25155-2026 artfynd.xlsx
+++ b/artfynd/A 25155-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114429</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117636</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1015,6 +1030,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74119948</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1126,6 +1146,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74119952</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1237,8 +1262,20 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74861045</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>